--- a/rules/CORE-000792/negative/01/data/unit-test-coreid-FB0905-negative.xlsx
+++ b/rules/CORE-000792/negative/01/data/unit-test-coreid-FB0905-negative.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="dm.xpt" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ce.xpt" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="cm.xpt" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="su.xpt" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dm.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ce.xpt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cm.xpt" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="su.xpt" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ag.xpt" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -69,7 +70,7 @@
       <sz val="7"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +99,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor theme="0" tint="-0.1499984740745262"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -158,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -226,6 +233,17 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -632,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,6 +710,18 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>Substance Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ag.xpt</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Agents</t>
         </is>
       </c>
     </row>
@@ -706,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,6 +768,388 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Error value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CMCLAS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NSAID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CMCLASCD</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>C3853540</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CMCLAS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NSAID</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CMCLASCD</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>C3853542</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CMCLAS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NSAID</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CMCLASCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CMCLAS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NSAID</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CMCLASCD</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>C3853545</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CMCLAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CMCLASCD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>C3853545</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>su.xpt</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SUCLAS</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CIGARETTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>su.xpt</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SUCLASCD</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>C42678</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>su.xpt</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SUCLAS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CIGARETTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>su.xpt</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SUCLASCD</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>C42679</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1697,7 @@
           <t>2006-04-01</t>
         </is>
       </c>
-      <c r="L5" s="9" t="n"/>
+      <c r="L5" s="6" t="n"/>
       <c r="M5" s="7" t="n">
         <v>701</v>
       </c>
@@ -1399,7 +1811,7 @@
           <t>2006-03-26</t>
         </is>
       </c>
-      <c r="L6" s="13" t="n"/>
+      <c r="L6" s="6" t="n"/>
       <c r="M6" s="11" t="n">
         <v>701</v>
       </c>
@@ -1613,7 +2025,7 @@
           <t>CETERM</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>CEDECOD</t>
         </is>
@@ -1722,7 +2134,7 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>DEATH</t>
         </is>
@@ -1753,7 +2165,7 @@
           <t>Dead</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>DEATH</t>
         </is>
@@ -2577,12 +2989,12 @@
           <t>ASPIRIN</t>
         </is>
       </c>
-      <c r="Q5" s="23" t="inlineStr">
+      <c r="Q5" s="27" t="inlineStr">
         <is>
           <t>NSAID</t>
         </is>
       </c>
-      <c r="R5" s="24" t="inlineStr">
+      <c r="R5" s="28" t="inlineStr">
         <is>
           <t>C3853540</t>
         </is>
@@ -2614,12 +3026,12 @@
           <t>ASPIRIN</t>
         </is>
       </c>
-      <c r="Q6" s="23" t="inlineStr">
+      <c r="Q6" s="27" t="inlineStr">
         <is>
           <t>NSAID</t>
         </is>
       </c>
-      <c r="R6" s="24" t="inlineStr">
+      <c r="R6" s="28" t="inlineStr">
         <is>
           <t>C3853542</t>
         </is>
@@ -2651,12 +3063,12 @@
           <t>ASPIRIN</t>
         </is>
       </c>
-      <c r="Q7" s="23" t="inlineStr">
+      <c r="Q7" s="27" t="inlineStr">
         <is>
           <t>NSAID</t>
         </is>
       </c>
-      <c r="R7" s="24" t="n"/>
+      <c r="R7" s="28" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -2684,12 +3096,12 @@
           <t>ASPIRIN</t>
         </is>
       </c>
-      <c r="Q8" s="23" t="inlineStr">
+      <c r="Q8" s="27" t="inlineStr">
         <is>
           <t>NSAID</t>
         </is>
       </c>
-      <c r="R8" s="24" t="inlineStr">
+      <c r="R8" s="28" t="inlineStr">
         <is>
           <t>C3853545</t>
         </is>
@@ -2721,8 +3133,8 @@
           <t>ASPIRIN</t>
         </is>
       </c>
-      <c r="Q9" s="23" t="n"/>
-      <c r="R9" s="24" t="inlineStr">
+      <c r="Q9" s="27" t="n"/>
+      <c r="R9" s="28" t="inlineStr">
         <is>
           <t>C3853545</t>
         </is>
@@ -3722,12 +4134,12 @@
           <t>CIGARETTES</t>
         </is>
       </c>
-      <c r="P5" s="26" t="inlineStr">
+      <c r="P5" s="29" t="inlineStr">
         <is>
           <t>CIGARETTE</t>
         </is>
       </c>
-      <c r="Q5" s="26" t="inlineStr">
+      <c r="Q5" s="29" t="inlineStr">
         <is>
           <t>C42678</t>
         </is>
@@ -3826,12 +4238,12 @@
           <t>CIGARETTES</t>
         </is>
       </c>
-      <c r="P7" s="26" t="inlineStr">
+      <c r="P7" s="29" t="inlineStr">
         <is>
           <t>CIGARETTE</t>
         </is>
       </c>
-      <c r="Q7" s="26" t="inlineStr">
+      <c r="Q7" s="29" t="inlineStr">
         <is>
           <t>C42679</t>
         </is>
@@ -3943,6 +4355,322 @@
       <c r="R9" s="18" t="inlineStr">
         <is>
           <t>3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>DOMAIN</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>AGSEQ</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>AGTRT</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>AGPRESP</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>AGOCCUR</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
+          <t>AGDOSE</t>
+        </is>
+      </c>
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t>AGDOSU</t>
+        </is>
+      </c>
+      <c r="J1" s="14" t="inlineStr">
+        <is>
+          <t>AGVAMT</t>
+        </is>
+      </c>
+      <c r="K1" s="14" t="inlineStr">
+        <is>
+          <t>AGVAMTU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Study Identifier</t>
+        </is>
+      </c>
+      <c r="B2" s="30" t="inlineStr">
+        <is>
+          <t>Domain Abbreviation</t>
+        </is>
+      </c>
+      <c r="C2" s="30" t="inlineStr">
+        <is>
+          <t>Unique Subject Identifier</t>
+        </is>
+      </c>
+      <c r="D2" s="30" t="inlineStr">
+        <is>
+          <t>Sequence Number</t>
+        </is>
+      </c>
+      <c r="E2" s="30" t="inlineStr">
+        <is>
+          <t>Reported Agent Name</t>
+        </is>
+      </c>
+      <c r="F2" s="30" t="inlineStr">
+        <is>
+          <t>AG Pre-Specified</t>
+        </is>
+      </c>
+      <c r="G2" s="30" t="inlineStr">
+        <is>
+          <t>AG Occurrence</t>
+        </is>
+      </c>
+      <c r="H2" s="30" t="inlineStr">
+        <is>
+          <t>Dose per Administration</t>
+        </is>
+      </c>
+      <c r="I2" s="30" t="inlineStr">
+        <is>
+          <t>Dose Units</t>
+        </is>
+      </c>
+      <c r="J2" s="30" t="inlineStr">
+        <is>
+          <t>Treatment Vehicle
+Amount</t>
+        </is>
+      </c>
+      <c r="K2" s="30" t="inlineStr">
+        <is>
+          <t>Treatment Vehicle
+Amount Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="30" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="30" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="30" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="E3" s="30" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="30" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="30" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H3" s="30" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="I3" s="30" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="30" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="K3" s="30" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="K4" s="30" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>XYZ-001-001</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Tuberculin PPD-S</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>tuberculin unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>XYZ-001-002</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Tuberculin PPD-S</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>tuberculin unit</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>mL</t>
         </is>
       </c>
     </row>
